--- a/pages/exoformule/formule.xlsx
+++ b/pages/exoformule/formule.xlsx
@@ -1,37 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cours\0- pédagogie\0 Paquetage scrom\SuperSite\pages\exoformule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3C1332-8F3E-4A26-AD33-BD063796FEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FCDE694-41D5-410E-A852-EB1E11848E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="3" xr2:uid="{265E9A38-2995-4177-9081-96CEA6BA5440}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{265E9A38-2995-4177-9081-96CEA6BA5440}"/>
   </bookViews>
   <sheets>
-    <sheet name="Mono" sheetId="1" r:id="rId1"/>
-    <sheet name="1" sheetId="2" r:id="rId2"/>
-    <sheet name="13" sheetId="3" r:id="rId3"/>
-    <sheet name="Continu" sheetId="4" r:id="rId4"/>
-    <sheet name="TRI" sheetId="5" r:id="rId5"/>
-    <sheet name="Mono H" sheetId="6" r:id="rId6"/>
-    <sheet name="T M" sheetId="7" r:id="rId7"/>
-    <sheet name="T Tri" sheetId="8" r:id="rId8"/>
-    <sheet name="41 T" sheetId="9" r:id="rId9"/>
-    <sheet name="41 R" sheetId="11" r:id="rId10"/>
-    <sheet name="42" sheetId="12" r:id="rId11"/>
-    <sheet name="5" sheetId="13" r:id="rId12"/>
-    <sheet name="6" sheetId="14" r:id="rId13"/>
-    <sheet name="62" sheetId="15" r:id="rId14"/>
-    <sheet name="71" sheetId="16" r:id="rId15"/>
-    <sheet name="72" sheetId="17" r:id="rId16"/>
-    <sheet name="73" sheetId="18" r:id="rId17"/>
-    <sheet name="8" sheetId="19" r:id="rId18"/>
+    <sheet name="Formule" sheetId="20" r:id="rId1"/>
+    <sheet name="Mono" sheetId="1" r:id="rId2"/>
+    <sheet name="1" sheetId="2" r:id="rId3"/>
+    <sheet name="13" sheetId="3" r:id="rId4"/>
+    <sheet name="Continu" sheetId="4" r:id="rId5"/>
+    <sheet name="TRI" sheetId="5" r:id="rId6"/>
+    <sheet name="Mono H" sheetId="6" r:id="rId7"/>
+    <sheet name="T M" sheetId="7" r:id="rId8"/>
+    <sheet name="T Tri" sheetId="8" r:id="rId9"/>
+    <sheet name="41 T" sheetId="9" r:id="rId10"/>
+    <sheet name="41 R" sheetId="11" r:id="rId11"/>
+    <sheet name="42" sheetId="12" r:id="rId12"/>
+    <sheet name="5" sheetId="13" r:id="rId13"/>
+    <sheet name="6" sheetId="14" r:id="rId14"/>
+    <sheet name="62" sheetId="15" r:id="rId15"/>
+    <sheet name="71" sheetId="16" r:id="rId16"/>
+    <sheet name="72" sheetId="17" r:id="rId17"/>
+    <sheet name="73" sheetId="18" r:id="rId18"/>
+    <sheet name="8" sheetId="19" r:id="rId19"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Formule!$F$1:$F$87</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -53,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2077" uniqueCount="1032">
   <si>
     <t>VI</t>
   </si>
@@ -2723,6 +2727,432 @@
   </si>
   <si>
     <t>1Ah</t>
+  </si>
+  <si>
+    <t>Rendement</t>
+  </si>
+  <si>
+    <t>\\%</t>
+  </si>
+  <si>
+    <t>sans~unité</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Energie absorbée</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>W/h</t>
+  </si>
+  <si>
+    <t>Energie utile</t>
+  </si>
+  <si>
+    <t>Energie perdue</t>
+  </si>
+  <si>
+    <t>Puissance absorbée</t>
+  </si>
+  <si>
+    <t>Puissance utile</t>
+  </si>
+  <si>
+    <t>Puissance perdue</t>
+  </si>
+  <si>
+    <t>Wh</t>
+  </si>
+  <si>
+    <t>Facteur de charge</t>
+  </si>
+  <si>
+    <t>Flux thermique</t>
+  </si>
+  <si>
+    <t>°</t>
+  </si>
+  <si>
+    <t>Résistance thermique</t>
+  </si>
+  <si>
+    <t>K/W</t>
+  </si>
+  <si>
+    <t>W/K</t>
+  </si>
+  <si>
+    <t>\\Omega</t>
+  </si>
+  <si>
+    <t>Température</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>°C</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Energie thermique</t>
+  </si>
+  <si>
+    <t>Débit massique</t>
+  </si>
+  <si>
+    <t>kg/s</t>
+  </si>
+  <si>
+    <t>kg/h</t>
+  </si>
+  <si>
+    <t>m^2/s</t>
+  </si>
+  <si>
+    <t>m^3/s</t>
+  </si>
+  <si>
+    <t>Débit volumique</t>
+  </si>
+  <si>
+    <t>m^3/h</t>
+  </si>
+  <si>
+    <t>Puissance thermique</t>
+  </si>
+  <si>
+    <t>Courant électrique</t>
+  </si>
+  <si>
+    <t>Tension électrique</t>
+  </si>
+  <si>
+    <t>Charge électrque</t>
+  </si>
+  <si>
+    <t>Ah</t>
+  </si>
+  <si>
+    <t>Puissance électrique</t>
+  </si>
+  <si>
+    <t>Energie électrique</t>
+  </si>
+  <si>
+    <t>Résistance</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Durée</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>Force électromotrice</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Nm</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>Fréquence</t>
+  </si>
+  <si>
+    <t>Pulsation</t>
+  </si>
+  <si>
+    <t>rad/s</t>
+  </si>
+  <si>
+    <t>rad</t>
+  </si>
+  <si>
+    <t>Période</t>
+  </si>
+  <si>
+    <t>Déphasage</t>
+  </si>
+  <si>
+    <t>Inductance</t>
+  </si>
+  <si>
+    <t>Capacité</t>
+  </si>
+  <si>
+    <t>Puissance active</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>vad</t>
+  </si>
+  <si>
+    <t>Puissance réactive</t>
+  </si>
+  <si>
+    <t>Puissance apparente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux de distorsion harmonique </t>
+  </si>
+  <si>
+    <t>Puissance déformante</t>
+  </si>
+  <si>
+    <t>Facteur de puissance</t>
+  </si>
+  <si>
+    <t>Déplacement du facteur de puissance</t>
+  </si>
+  <si>
+    <t>Rapport de transformation</t>
+  </si>
+  <si>
+    <t>Pertes joules</t>
+  </si>
+  <si>
+    <t>Pertes ferromagnétiques</t>
+  </si>
+  <si>
+    <t>Impédance</t>
+  </si>
+  <si>
+    <t>Réactance</t>
+  </si>
+  <si>
+    <t>Masse</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Moment d'intertie</t>
+  </si>
+  <si>
+    <t>kg \\cdot m^2</t>
+  </si>
+  <si>
+    <t>kg /m^2</t>
+  </si>
+  <si>
+    <t>Masse volumique</t>
+  </si>
+  <si>
+    <t>kg \\cdot m^3</t>
+  </si>
+  <si>
+    <t>kg \\cdot m^{-3}</t>
+  </si>
+  <si>
+    <t>kg \\cdot m^{-2}</t>
+  </si>
+  <si>
+    <t>Force</t>
+  </si>
+  <si>
+    <t>Pa</t>
+  </si>
+  <si>
+    <t>Couple</t>
+  </si>
+  <si>
+    <t>Accélération</t>
+  </si>
+  <si>
+    <t>m \\cdot s^{-2}</t>
+  </si>
+  <si>
+    <t>m \\cdot s^{-1}</t>
+  </si>
+  <si>
+    <t>m/s</t>
+  </si>
+  <si>
+    <t>Accélération angulaire</t>
+  </si>
+  <si>
+    <t>rad \\cdot s^{-2}</t>
+  </si>
+  <si>
+    <t>Vitesse</t>
+  </si>
+  <si>
+    <t>km/h</t>
+  </si>
+  <si>
+    <t>Vitesse angulaire</t>
+  </si>
+  <si>
+    <t>rad \\cdot s^{-1}</t>
+  </si>
+  <si>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>Position angulaire</t>
+  </si>
+  <si>
+    <t>Energie cinétique</t>
+  </si>
+  <si>
+    <t>Energie potentielle</t>
+  </si>
+  <si>
+    <t>Travail d'une force</t>
+  </si>
+  <si>
+    <t>Puissance mécanique</t>
+  </si>
+  <si>
+    <t>Poids</t>
+  </si>
+  <si>
+    <t>Pression</t>
+  </si>
+  <si>
+    <t>bar</t>
+  </si>
+  <si>
+    <t>Surface</t>
+  </si>
+  <si>
+    <t>m^2</t>
+  </si>
+  <si>
+    <t>m^3</t>
+  </si>
+  <si>
+    <t>m^4</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Hauteur</t>
+  </si>
+  <si>
+    <t>Diamètre</t>
+  </si>
+  <si>
+    <t>Rayon</t>
+  </si>
+  <si>
+    <t>\\pi</t>
+  </si>
+  <si>
+    <t>Profondeur de décharge</t>
+  </si>
+  <si>
+    <t>Etat de charge</t>
+  </si>
+  <si>
+    <t>Capacité d'une batterie</t>
+  </si>
+  <si>
+    <t>A/h</t>
+  </si>
+  <si>
+    <t>Tension nominale</t>
+  </si>
+  <si>
+    <t>Courant nominal</t>
+  </si>
+  <si>
+    <t>Longueur d'onde</t>
+  </si>
+  <si>
+    <t>Température de couleur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">° </t>
+  </si>
+  <si>
+    <t>Intensité lumineuse</t>
+  </si>
+  <si>
+    <t>Cd</t>
+  </si>
+  <si>
+    <t>Lm</t>
+  </si>
+  <si>
+    <t>lux</t>
+  </si>
+  <si>
+    <t>Indice de rendu des couleurs</t>
+  </si>
+  <si>
+    <t>Flux lumineux</t>
+  </si>
+  <si>
+    <t>W/m^2</t>
+  </si>
+  <si>
+    <t>Efficacité lumineuse</t>
+  </si>
+  <si>
+    <t>Lm/W</t>
+  </si>
+  <si>
+    <t>W/Lm</t>
+  </si>
+  <si>
+    <t>Eclairement</t>
+  </si>
+  <si>
+    <t>Cd/m^2</t>
+  </si>
+  <si>
+    <t>Uniformité</t>
+  </si>
+  <si>
+    <t>Luminance</t>
+  </si>
+  <si>
+    <t>Irradiance</t>
+  </si>
+  <si>
+    <t>Puissance électromagnétique</t>
+  </si>
+  <si>
+    <t>A/m</t>
+  </si>
+  <si>
+    <t>Champ magnétique</t>
+  </si>
+  <si>
+    <t>Glissement</t>
+  </si>
+  <si>
+    <t>tr/min</t>
+  </si>
+  <si>
+    <t>rad \\cdot s</t>
+  </si>
+  <si>
+    <t>Couple utile</t>
   </si>
 </sst>
 </file>
@@ -3104,6 +3534,4280 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{669D93D0-CDF3-4BC4-B48B-8587E00099B5}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C1" t="s">
+        <v>891</v>
+      </c>
+      <c r="D1" t="s">
+        <v>640</v>
+      </c>
+      <c r="E1" t="s">
+        <v>893</v>
+      </c>
+      <c r="F1">
+        <v>1</v>
+      </c>
+      <c r="H1">
+        <f>COUNTIF(F1:F2000,1)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B2" t="s">
+        <v>893</v>
+      </c>
+      <c r="C2" t="s">
+        <v>640</v>
+      </c>
+      <c r="D2" t="s">
+        <v>902</v>
+      </c>
+      <c r="E2" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <f>COUNTIF(F1:F4000,2)</f>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>897</v>
+      </c>
+      <c r="B3" t="s">
+        <v>893</v>
+      </c>
+      <c r="C3" t="s">
+        <v>640</v>
+      </c>
+      <c r="D3" t="s">
+        <v>902</v>
+      </c>
+      <c r="E3" t="s">
+        <v>896</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>898</v>
+      </c>
+      <c r="B4" t="s">
+        <v>893</v>
+      </c>
+      <c r="C4" t="s">
+        <v>640</v>
+      </c>
+      <c r="D4" t="s">
+        <v>902</v>
+      </c>
+      <c r="E4" t="s">
+        <v>896</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>899</v>
+      </c>
+      <c r="B5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C5" t="s">
+        <v>893</v>
+      </c>
+      <c r="D5" t="s">
+        <v>902</v>
+      </c>
+      <c r="E5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>900</v>
+      </c>
+      <c r="B6" t="s">
+        <v>640</v>
+      </c>
+      <c r="C6" t="s">
+        <v>893</v>
+      </c>
+      <c r="D6" t="s">
+        <v>902</v>
+      </c>
+      <c r="E6" t="s">
+        <v>896</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>901</v>
+      </c>
+      <c r="B7" t="s">
+        <v>640</v>
+      </c>
+      <c r="C7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D7" t="s">
+        <v>902</v>
+      </c>
+      <c r="E7" t="s">
+        <v>896</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>903</v>
+      </c>
+      <c r="B8" t="s">
+        <v>892</v>
+      </c>
+      <c r="C8" t="s">
+        <v>891</v>
+      </c>
+      <c r="D8" t="s">
+        <v>640</v>
+      </c>
+      <c r="E8" t="s">
+        <v>893</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>904</v>
+      </c>
+      <c r="B9" t="s">
+        <v>640</v>
+      </c>
+      <c r="C9" t="s">
+        <v>893</v>
+      </c>
+      <c r="D9" t="s">
+        <v>895</v>
+      </c>
+      <c r="E9" t="s">
+        <v>905</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>906</v>
+      </c>
+      <c r="B10" t="s">
+        <v>907</v>
+      </c>
+      <c r="C10" t="s">
+        <v>908</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E10" t="s">
+        <v>896</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>910</v>
+      </c>
+      <c r="B11" t="s">
+        <v>911</v>
+      </c>
+      <c r="C11" t="s">
+        <v>905</v>
+      </c>
+      <c r="D11" t="s">
+        <v>515</v>
+      </c>
+      <c r="E11" t="s">
+        <v>913</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>914</v>
+      </c>
+      <c r="B12" t="s">
+        <v>893</v>
+      </c>
+      <c r="C12" t="s">
+        <v>902</v>
+      </c>
+      <c r="D12" t="s">
+        <v>911</v>
+      </c>
+      <c r="E12" t="s">
+        <v>912</v>
+      </c>
+      <c r="F12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>915</v>
+      </c>
+      <c r="B13" t="s">
+        <v>916</v>
+      </c>
+      <c r="C13" t="s">
+        <v>917</v>
+      </c>
+      <c r="D13" t="s">
+        <v>918</v>
+      </c>
+      <c r="E13" t="s">
+        <v>919</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>920</v>
+      </c>
+      <c r="B14" t="s">
+        <v>919</v>
+      </c>
+      <c r="C14" t="s">
+        <v>921</v>
+      </c>
+      <c r="D14" t="s">
+        <v>916</v>
+      </c>
+      <c r="E14" t="s">
+        <v>918</v>
+      </c>
+      <c r="F14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>922</v>
+      </c>
+      <c r="B15" t="s">
+        <v>640</v>
+      </c>
+      <c r="C15" t="s">
+        <v>893</v>
+      </c>
+      <c r="D15" t="s">
+        <v>902</v>
+      </c>
+      <c r="E15" t="s">
+        <v>896</v>
+      </c>
+      <c r="F15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>923</v>
+      </c>
+      <c r="B16" t="s">
+        <v>895</v>
+      </c>
+      <c r="C16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" t="s">
+        <v>640</v>
+      </c>
+      <c r="E16" t="s">
+        <v>629</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>924</v>
+      </c>
+      <c r="B17" t="s">
+        <v>629</v>
+      </c>
+      <c r="C17" t="s">
+        <v>895</v>
+      </c>
+      <c r="D17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E17" t="s">
+        <v>640</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>925</v>
+      </c>
+      <c r="B18" t="s">
+        <v>73</v>
+      </c>
+      <c r="C18" t="s">
+        <v>926</v>
+      </c>
+      <c r="D18" t="s">
+        <v>629</v>
+      </c>
+      <c r="E18" t="s">
+        <v>895</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>927</v>
+      </c>
+      <c r="B19" t="s">
+        <v>640</v>
+      </c>
+      <c r="C19" t="s">
+        <v>893</v>
+      </c>
+      <c r="D19" t="s">
+        <v>902</v>
+      </c>
+      <c r="E19" t="s">
+        <v>896</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>928</v>
+      </c>
+      <c r="B20" t="s">
+        <v>893</v>
+      </c>
+      <c r="C20" t="s">
+        <v>640</v>
+      </c>
+      <c r="D20" t="s">
+        <v>902</v>
+      </c>
+      <c r="E20" t="s">
+        <v>896</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>929</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C21" t="s">
+        <v>517</v>
+      </c>
+      <c r="D21" t="s">
+        <v>930</v>
+      </c>
+      <c r="E21" t="s">
+        <v>907</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>931</v>
+      </c>
+      <c r="B22" t="s">
+        <v>913</v>
+      </c>
+      <c r="C22" t="s">
+        <v>932</v>
+      </c>
+      <c r="D22" t="s">
+        <v>933</v>
+      </c>
+      <c r="E22" t="s">
+        <v>515</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>934</v>
+      </c>
+      <c r="B23" t="s">
+        <v>629</v>
+      </c>
+      <c r="C23" t="s">
+        <v>935</v>
+      </c>
+      <c r="D23" t="s">
+        <v>936</v>
+      </c>
+      <c r="E23" t="s">
+        <v>895</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>938</v>
+      </c>
+      <c r="B24" t="s">
+        <v>937</v>
+      </c>
+      <c r="C24" t="s">
+        <v>913</v>
+      </c>
+      <c r="D24" t="s">
+        <v>515</v>
+      </c>
+      <c r="E24" t="s">
+        <v>629</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>939</v>
+      </c>
+      <c r="B25" t="s">
+        <v>940</v>
+      </c>
+      <c r="C25" t="s">
+        <v>941</v>
+      </c>
+      <c r="D25" t="s">
+        <v>913</v>
+      </c>
+      <c r="E25" t="s">
+        <v>937</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>942</v>
+      </c>
+      <c r="B26" t="s">
+        <v>913</v>
+      </c>
+      <c r="C26" t="s">
+        <v>932</v>
+      </c>
+      <c r="D26" t="s">
+        <v>941</v>
+      </c>
+      <c r="E26" t="s">
+        <v>515</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>943</v>
+      </c>
+      <c r="B27" t="s">
+        <v>905</v>
+      </c>
+      <c r="C27" t="s">
+        <v>912</v>
+      </c>
+      <c r="D27" t="s">
+        <v>913</v>
+      </c>
+      <c r="E27" t="s">
+        <v>940</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>944</v>
+      </c>
+      <c r="B28" t="s">
+        <v>930</v>
+      </c>
+      <c r="C28" t="s">
+        <v>517</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E28" t="s">
+        <v>937</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>945</v>
+      </c>
+      <c r="B29" t="s">
+        <v>517</v>
+      </c>
+      <c r="C29" t="s">
+        <v>930</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E29" t="s">
+        <v>937</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>946</v>
+      </c>
+      <c r="B30" t="s">
+        <v>640</v>
+      </c>
+      <c r="C30" t="s">
+        <v>947</v>
+      </c>
+      <c r="D30" t="s">
+        <v>948</v>
+      </c>
+      <c r="E30" t="s">
+        <v>893</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>950</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D31" t="s">
+        <v>948</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>951</v>
+      </c>
+      <c r="B32" t="s">
+        <v>948</v>
+      </c>
+      <c r="C32" t="s">
+        <v>947</v>
+      </c>
+      <c r="D32" t="s">
+        <v>640</v>
+      </c>
+      <c r="E32" t="s">
+        <v>902</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>954</v>
+      </c>
+      <c r="B33" t="s">
+        <v>892</v>
+      </c>
+      <c r="C33" t="s">
+        <v>891</v>
+      </c>
+      <c r="D33" t="s">
+        <v>640</v>
+      </c>
+      <c r="E33" t="s">
+        <v>902</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>928</v>
+      </c>
+      <c r="B34" t="s">
+        <v>893</v>
+      </c>
+      <c r="C34" t="s">
+        <v>902</v>
+      </c>
+      <c r="D34" t="s">
+        <v>629</v>
+      </c>
+      <c r="E34" t="s">
+        <v>895</v>
+      </c>
+      <c r="F34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>952</v>
+      </c>
+      <c r="B35" t="s">
+        <v>892</v>
+      </c>
+      <c r="C35" t="s">
+        <v>891</v>
+      </c>
+      <c r="D35" t="s">
+        <v>629</v>
+      </c>
+      <c r="E35" t="s">
+        <v>895</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>946</v>
+      </c>
+      <c r="B36" t="s">
+        <v>640</v>
+      </c>
+      <c r="C36" t="s">
+        <v>947</v>
+      </c>
+      <c r="D36" t="s">
+        <v>948</v>
+      </c>
+      <c r="E36" t="s">
+        <v>949</v>
+      </c>
+      <c r="F36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>950</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D37" t="s">
+        <v>948</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="F37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>951</v>
+      </c>
+      <c r="B38" t="s">
+        <v>948</v>
+      </c>
+      <c r="C38" t="s">
+        <v>947</v>
+      </c>
+      <c r="D38" t="s">
+        <v>640</v>
+      </c>
+      <c r="E38" t="s">
+        <v>949</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>953</v>
+      </c>
+      <c r="B39" t="s">
+        <v>949</v>
+      </c>
+      <c r="C39" t="s">
+        <v>948</v>
+      </c>
+      <c r="D39" t="s">
+        <v>947</v>
+      </c>
+      <c r="E39" t="s">
+        <v>640</v>
+      </c>
+      <c r="F39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>955</v>
+      </c>
+      <c r="B40" t="s">
+        <v>892</v>
+      </c>
+      <c r="C40" t="s">
+        <v>891</v>
+      </c>
+      <c r="D40" t="s">
+        <v>629</v>
+      </c>
+      <c r="E40" t="s">
+        <v>895</v>
+      </c>
+      <c r="F40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>956</v>
+      </c>
+      <c r="B41" t="s">
+        <v>892</v>
+      </c>
+      <c r="C41" t="s">
+        <v>891</v>
+      </c>
+      <c r="D41" t="s">
+        <v>629</v>
+      </c>
+      <c r="E41" t="s">
+        <v>895</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>957</v>
+      </c>
+      <c r="B42" t="s">
+        <v>640</v>
+      </c>
+      <c r="C42" t="s">
+        <v>893</v>
+      </c>
+      <c r="D42" t="s">
+        <v>902</v>
+      </c>
+      <c r="E42" t="s">
+        <v>895</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>958</v>
+      </c>
+      <c r="B43" t="s">
+        <v>640</v>
+      </c>
+      <c r="C43" t="s">
+        <v>893</v>
+      </c>
+      <c r="D43" t="s">
+        <v>902</v>
+      </c>
+      <c r="E43" t="s">
+        <v>895</v>
+      </c>
+      <c r="F43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>959</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C44" t="s">
+        <v>517</v>
+      </c>
+      <c r="D44" t="s">
+        <v>930</v>
+      </c>
+      <c r="E44" t="s">
+        <v>907</v>
+      </c>
+      <c r="F44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>960</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C45" t="s">
+        <v>517</v>
+      </c>
+      <c r="D45" t="s">
+        <v>930</v>
+      </c>
+      <c r="E45" t="s">
+        <v>907</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>961</v>
+      </c>
+      <c r="B46" t="s">
+        <v>962</v>
+      </c>
+      <c r="C46" t="s">
+        <v>532</v>
+      </c>
+      <c r="D46" t="s">
+        <v>935</v>
+      </c>
+      <c r="E46" t="s">
+        <v>936</v>
+      </c>
+      <c r="F46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>963</v>
+      </c>
+      <c r="B47" t="s">
+        <v>964</v>
+      </c>
+      <c r="C47" t="s">
+        <v>965</v>
+      </c>
+      <c r="D47" t="s">
+        <v>969</v>
+      </c>
+      <c r="E47" t="s">
+        <v>936</v>
+      </c>
+      <c r="F47">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>966</v>
+      </c>
+      <c r="B48" t="s">
+        <v>968</v>
+      </c>
+      <c r="C48" t="s">
+        <v>965</v>
+      </c>
+      <c r="D48" t="s">
+        <v>962</v>
+      </c>
+      <c r="E48" t="s">
+        <v>967</v>
+      </c>
+      <c r="F48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>970</v>
+      </c>
+      <c r="B49" t="s">
+        <v>935</v>
+      </c>
+      <c r="C49" t="s">
+        <v>936</v>
+      </c>
+      <c r="D49" t="s">
+        <v>962</v>
+      </c>
+      <c r="E49" t="s">
+        <v>971</v>
+      </c>
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>972</v>
+      </c>
+      <c r="B50" t="s">
+        <v>936</v>
+      </c>
+      <c r="C50" t="s">
+        <v>935</v>
+      </c>
+      <c r="D50" t="s">
+        <v>962</v>
+      </c>
+      <c r="E50" t="s">
+        <v>971</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>973</v>
+      </c>
+      <c r="B51" t="s">
+        <v>974</v>
+      </c>
+      <c r="C51" t="s">
+        <v>975</v>
+      </c>
+      <c r="D51" t="s">
+        <v>976</v>
+      </c>
+      <c r="E51" t="s">
+        <v>940</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>977</v>
+      </c>
+      <c r="B52" t="s">
+        <v>978</v>
+      </c>
+      <c r="C52" t="s">
+        <v>974</v>
+      </c>
+      <c r="D52" t="s">
+        <v>976</v>
+      </c>
+      <c r="E52" t="s">
+        <v>940</v>
+      </c>
+      <c r="F52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>979</v>
+      </c>
+      <c r="B53" t="s">
+        <v>975</v>
+      </c>
+      <c r="C53" t="s">
+        <v>974</v>
+      </c>
+      <c r="D53" t="s">
+        <v>980</v>
+      </c>
+      <c r="E53" t="s">
+        <v>940</v>
+      </c>
+      <c r="F53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>981</v>
+      </c>
+      <c r="B54" t="s">
+        <v>982</v>
+      </c>
+      <c r="C54" t="s">
+        <v>974</v>
+      </c>
+      <c r="D54" t="s">
+        <v>976</v>
+      </c>
+      <c r="E54" t="s">
+        <v>978</v>
+      </c>
+      <c r="F54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>983</v>
+      </c>
+      <c r="B55" t="s">
+        <v>515</v>
+      </c>
+      <c r="C55" t="s">
+        <v>941</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E55" t="s">
+        <v>892</v>
+      </c>
+      <c r="F55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>984</v>
+      </c>
+      <c r="B56" t="s">
+        <v>941</v>
+      </c>
+      <c r="C56" t="s">
+        <v>515</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="E56" t="s">
+        <v>892</v>
+      </c>
+      <c r="F56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>985</v>
+      </c>
+      <c r="B57" t="s">
+        <v>893</v>
+      </c>
+      <c r="C57" t="s">
+        <v>902</v>
+      </c>
+      <c r="D57" t="s">
+        <v>640</v>
+      </c>
+      <c r="E57" t="s">
+        <v>896</v>
+      </c>
+      <c r="F57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>986</v>
+      </c>
+      <c r="B58" t="s">
+        <v>893</v>
+      </c>
+      <c r="C58" t="s">
+        <v>902</v>
+      </c>
+      <c r="D58" t="s">
+        <v>640</v>
+      </c>
+      <c r="E58" t="s">
+        <v>896</v>
+      </c>
+      <c r="F58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>987</v>
+      </c>
+      <c r="B59" t="s">
+        <v>893</v>
+      </c>
+      <c r="C59" t="s">
+        <v>902</v>
+      </c>
+      <c r="D59" t="s">
+        <v>936</v>
+      </c>
+      <c r="E59" t="s">
+        <v>935</v>
+      </c>
+      <c r="F59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>988</v>
+      </c>
+      <c r="B60" t="s">
+        <v>640</v>
+      </c>
+      <c r="C60" t="s">
+        <v>893</v>
+      </c>
+      <c r="D60" t="s">
+        <v>902</v>
+      </c>
+      <c r="E60" t="s">
+        <v>896</v>
+      </c>
+      <c r="F60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>989</v>
+      </c>
+      <c r="B61" t="s">
+        <v>935</v>
+      </c>
+      <c r="C61" t="s">
+        <v>936</v>
+      </c>
+      <c r="D61" t="s">
+        <v>962</v>
+      </c>
+      <c r="E61" t="s">
+        <v>971</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>990</v>
+      </c>
+      <c r="B62" t="s">
+        <v>971</v>
+      </c>
+      <c r="C62" t="s">
+        <v>991</v>
+      </c>
+      <c r="D62" t="s">
+        <v>935</v>
+      </c>
+      <c r="E62" t="s">
+        <v>936</v>
+      </c>
+      <c r="F62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>992</v>
+      </c>
+      <c r="B63" t="s">
+        <v>993</v>
+      </c>
+      <c r="C63" t="s">
+        <v>515</v>
+      </c>
+      <c r="D63" t="s">
+        <v>994</v>
+      </c>
+      <c r="E63" t="s">
+        <v>995</v>
+      </c>
+      <c r="F63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>996</v>
+      </c>
+      <c r="B64" t="s">
+        <v>994</v>
+      </c>
+      <c r="C64" t="s">
+        <v>515</v>
+      </c>
+      <c r="D64" t="s">
+        <v>993</v>
+      </c>
+      <c r="E64" t="s">
+        <v>995</v>
+      </c>
+      <c r="F64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>997</v>
+      </c>
+      <c r="B65" t="s">
+        <v>515</v>
+      </c>
+      <c r="C65" t="s">
+        <v>913</v>
+      </c>
+      <c r="D65" t="s">
+        <v>993</v>
+      </c>
+      <c r="E65" t="s">
+        <v>994</v>
+      </c>
+      <c r="F65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>998</v>
+      </c>
+      <c r="B66" t="s">
+        <v>515</v>
+      </c>
+      <c r="C66" t="s">
+        <v>913</v>
+      </c>
+      <c r="D66" t="s">
+        <v>993</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>999</v>
+      </c>
+      <c r="B67" t="s">
+        <v>515</v>
+      </c>
+      <c r="C67" t="s">
+        <v>913</v>
+      </c>
+      <c r="D67" t="s">
+        <v>993</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B68" t="s">
+        <v>892</v>
+      </c>
+      <c r="C68" t="s">
+        <v>891</v>
+      </c>
+      <c r="D68" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" t="s">
+        <v>926</v>
+      </c>
+      <c r="F68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B69" t="s">
+        <v>892</v>
+      </c>
+      <c r="C69" t="s">
+        <v>891</v>
+      </c>
+      <c r="D69" t="s">
+        <v>73</v>
+      </c>
+      <c r="E69" t="s">
+        <v>926</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" t="s">
+        <v>926</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E70" t="s">
+        <v>893</v>
+      </c>
+      <c r="F70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B71" t="s">
+        <v>629</v>
+      </c>
+      <c r="C71" t="s">
+        <v>895</v>
+      </c>
+      <c r="D71" t="s">
+        <v>640</v>
+      </c>
+      <c r="E71" t="s">
+        <v>902</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B72" t="s">
+        <v>895</v>
+      </c>
+      <c r="C72" t="s">
+        <v>629</v>
+      </c>
+      <c r="D72" t="s">
+        <v>640</v>
+      </c>
+      <c r="E72" t="s">
+        <v>902</v>
+      </c>
+      <c r="F72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B73" t="s">
+        <v>515</v>
+      </c>
+      <c r="C73" t="s">
+        <v>937</v>
+      </c>
+      <c r="D73" t="s">
+        <v>913</v>
+      </c>
+      <c r="E73" t="s">
+        <v>976</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B74" t="s">
+        <v>911</v>
+      </c>
+      <c r="C74" t="s">
+        <v>912</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E74" t="s">
+        <v>640</v>
+      </c>
+      <c r="F74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C75" t="s">
+        <v>895</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B76" t="s">
+        <v>892</v>
+      </c>
+      <c r="C76" t="s">
+        <v>891</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C77" t="s">
+        <v>640</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E77" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D78" t="s">
+        <v>891</v>
+      </c>
+      <c r="E78" t="s">
+        <v>892</v>
+      </c>
+      <c r="F78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C79" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D79" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B80" t="s">
+        <v>892</v>
+      </c>
+      <c r="C80" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D80" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E80" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D81" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E81" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C82" t="s">
+        <v>640</v>
+      </c>
+      <c r="D82" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E82" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F82">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B83" t="s">
+        <v>640</v>
+      </c>
+      <c r="C83" t="s">
+        <v>659</v>
+      </c>
+      <c r="D83" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E83" t="s">
+        <v>895</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B84" t="s">
+        <v>659</v>
+      </c>
+      <c r="C84" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D84" t="s">
+        <v>640</v>
+      </c>
+      <c r="E84" t="s">
+        <v>895</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B85" t="s">
+        <v>892</v>
+      </c>
+      <c r="C85" t="s">
+        <v>891</v>
+      </c>
+      <c r="D85" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E85" t="s">
+        <v>940</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>981</v>
+      </c>
+      <c r="B86" t="s">
+        <v>940</v>
+      </c>
+      <c r="C86" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D86" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E86" t="s">
+        <v>941</v>
+      </c>
+      <c r="F86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B87" t="s">
+        <v>936</v>
+      </c>
+      <c r="C87" t="s">
+        <v>935</v>
+      </c>
+      <c r="D87" t="s">
+        <v>895</v>
+      </c>
+      <c r="E87" t="s">
+        <v>640</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="F1:F87" xr:uid="{669D93D0-CDF3-4BC4-B48B-8587E00099B5}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="D10" r:id="rId1" xr:uid="{F606A68D-B9C3-4A2F-AC76-ED1BCCAE7BF9}"/>
+    <hyperlink ref="B21" r:id="rId2" xr:uid="{0B14BF1A-7AF6-4B31-9902-B45484908D3F}"/>
+    <hyperlink ref="D28" r:id="rId3" xr:uid="{B3D56526-50DE-478A-A955-C11D1D3E7E24}"/>
+    <hyperlink ref="D29" r:id="rId4" xr:uid="{940DC72E-C09B-4AB9-B023-1EB8A4DF0226}"/>
+    <hyperlink ref="B44" r:id="rId5" xr:uid="{6A8950B2-232F-4580-992A-705C3E30CE98}"/>
+    <hyperlink ref="B45" r:id="rId6" xr:uid="{9175639F-A79C-4631-8F34-25B8A7CB1E5D}"/>
+    <hyperlink ref="D55" r:id="rId7" xr:uid="{854DAA68-CA4C-4B4B-BB57-B4EF77F11223}"/>
+    <hyperlink ref="D56" r:id="rId8" xr:uid="{2D7335CE-D5E2-4347-9D48-FD0A34333FDC}"/>
+    <hyperlink ref="E66" r:id="rId9" xr:uid="{84768C57-ED74-40B2-91E1-29A7013E0D58}"/>
+    <hyperlink ref="E67" r:id="rId10" xr:uid="{762D6EF9-6052-4E46-AC76-277C6E49B522}"/>
+    <hyperlink ref="D76" r:id="rId11" display="\\Omega" xr:uid="{5A7CEEDB-569B-446F-9A84-7ECE51A96418}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40EA02D-DC56-4A89-98F7-42A234EB60C7}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" t="s">
+        <v>494</v>
+      </c>
+      <c r="C2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E2" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>498</v>
+      </c>
+      <c r="B3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C3" t="s">
+        <v>502</v>
+      </c>
+      <c r="D3" t="s">
+        <v>499</v>
+      </c>
+      <c r="E3" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D4" t="s">
+        <v>503</v>
+      </c>
+      <c r="E4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+      <c r="C5" t="s">
+        <v>507</v>
+      </c>
+      <c r="D5" t="s">
+        <v>508</v>
+      </c>
+      <c r="E5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="B6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" t="s">
+        <v>512</v>
+      </c>
+      <c r="D6" t="s">
+        <v>513</v>
+      </c>
+      <c r="E6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>865</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="C7" t="s">
+        <v>516</v>
+      </c>
+      <c r="D7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B8" t="s">
+        <v>519</v>
+      </c>
+      <c r="C8" t="s">
+        <v>520</v>
+      </c>
+      <c r="D8" t="s">
+        <v>521</v>
+      </c>
+      <c r="E8" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>523</v>
+      </c>
+      <c r="B9" t="s">
+        <v>521</v>
+      </c>
+      <c r="C9" t="s">
+        <v>520</v>
+      </c>
+      <c r="D9" t="s">
+        <v>519</v>
+      </c>
+      <c r="E9" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>525</v>
+      </c>
+      <c r="B10" t="s">
+        <v>522</v>
+      </c>
+      <c r="C10" t="s">
+        <v>521</v>
+      </c>
+      <c r="D10" t="s">
+        <v>519</v>
+      </c>
+      <c r="E10" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>526</v>
+      </c>
+      <c r="B11" t="s">
+        <v>527</v>
+      </c>
+      <c r="C11" t="s">
+        <v>531</v>
+      </c>
+      <c r="D11" t="s">
+        <v>528</v>
+      </c>
+      <c r="E11" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>530</v>
+      </c>
+      <c r="B12" t="s">
+        <v>531</v>
+      </c>
+      <c r="C12" t="s">
+        <v>515</v>
+      </c>
+      <c r="D12" t="s">
+        <v>532</v>
+      </c>
+      <c r="E12" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>533</v>
+      </c>
+      <c r="B13" t="s">
+        <v>534</v>
+      </c>
+      <c r="C13" t="s">
+        <v>535</v>
+      </c>
+      <c r="D13" t="s">
+        <v>531</v>
+      </c>
+      <c r="E13" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>585</v>
+      </c>
+      <c r="B14" t="s">
+        <v>586</v>
+      </c>
+      <c r="C14" t="s">
+        <v>587</v>
+      </c>
+      <c r="D14" t="s">
+        <v>588</v>
+      </c>
+      <c r="E14" t="s">
+        <v>589</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" xr:uid="{FEC73E89-5B41-4E91-B6E2-A2658C373BCC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4AF2B7-091E-41FA-A36B-72547CA4D295}">
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B1" t="s">
+        <v>489</v>
+      </c>
+      <c r="C1" t="s">
+        <v>490</v>
+      </c>
+      <c r="D1" t="s">
+        <v>491</v>
+      </c>
+      <c r="E1" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B3" t="s">
+        <v>494</v>
+      </c>
+      <c r="C3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D3" t="s">
+        <v>496</v>
+      </c>
+      <c r="E3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>541</v>
+      </c>
+      <c r="B4" t="s">
+        <v>542</v>
+      </c>
+      <c r="C4" t="s">
+        <v>543</v>
+      </c>
+      <c r="D4" t="s">
+        <v>517</v>
+      </c>
+      <c r="E4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>550</v>
+      </c>
+      <c r="B5" t="s">
+        <v>554</v>
+      </c>
+      <c r="C5" t="s">
+        <v>547</v>
+      </c>
+      <c r="D5" t="s">
+        <v>545</v>
+      </c>
+      <c r="E5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>867</v>
+      </c>
+      <c r="B6" t="s">
+        <v>547</v>
+      </c>
+      <c r="C6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>551</v>
+      </c>
+      <c r="B7" t="s">
+        <v>552</v>
+      </c>
+      <c r="C7" t="s">
+        <v>553</v>
+      </c>
+      <c r="D7" t="s">
+        <v>554</v>
+      </c>
+      <c r="E7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="B8" t="s">
+        <v>557</v>
+      </c>
+      <c r="C8" t="s">
+        <v>558</v>
+      </c>
+      <c r="D8" t="s">
+        <v>559</v>
+      </c>
+      <c r="E8" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>561</v>
+      </c>
+      <c r="B9" t="s">
+        <v>516</v>
+      </c>
+      <c r="C9" t="s">
+        <v>562</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>524</v>
+      </c>
+      <c r="B10" t="s">
+        <v>563</v>
+      </c>
+      <c r="C10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D10" t="s">
+        <v>521</v>
+      </c>
+      <c r="E10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>525</v>
+      </c>
+      <c r="B11" t="s">
+        <v>565</v>
+      </c>
+      <c r="C11" t="s">
+        <v>521</v>
+      </c>
+      <c r="D11" t="s">
+        <v>566</v>
+      </c>
+      <c r="E11" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" t="s">
+        <v>566</v>
+      </c>
+      <c r="C12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D12" t="s">
+        <v>522</v>
+      </c>
+      <c r="E12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>567</v>
+      </c>
+      <c r="B13" t="s">
+        <v>568</v>
+      </c>
+      <c r="C13" t="s">
+        <v>569</v>
+      </c>
+      <c r="D13" t="s">
+        <v>570</v>
+      </c>
+      <c r="E13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>571</v>
+      </c>
+      <c r="B14" t="s">
+        <v>572</v>
+      </c>
+      <c r="C14" t="s">
+        <v>573</v>
+      </c>
+      <c r="D14" t="s">
+        <v>575</v>
+      </c>
+      <c r="E14" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>585</v>
+      </c>
+      <c r="B15" t="s">
+        <v>586</v>
+      </c>
+      <c r="C15" t="s">
+        <v>587</v>
+      </c>
+      <c r="D15" t="s">
+        <v>588</v>
+      </c>
+      <c r="E15" t="s">
+        <v>589</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A8" r:id="rId1" xr:uid="{9AED4FB5-E535-47E0-B49B-11BCE2A9FA4A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD96C3AE-00CF-4B4E-AD9B-52BC273DAF9D}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B1" t="s">
+        <v>577</v>
+      </c>
+      <c r="C1" t="s">
+        <v>578</v>
+      </c>
+      <c r="D1" t="s">
+        <v>579</v>
+      </c>
+      <c r="E1" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B2" t="s">
+        <v>582</v>
+      </c>
+      <c r="C2" t="s">
+        <v>583</v>
+      </c>
+      <c r="D2" t="s">
+        <v>584</v>
+      </c>
+      <c r="E2" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B3" t="s">
+        <v>586</v>
+      </c>
+      <c r="C3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D3" t="s">
+        <v>588</v>
+      </c>
+      <c r="E3" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E4" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>592</v>
+      </c>
+      <c r="B6" t="s">
+        <v>593</v>
+      </c>
+      <c r="C6" t="s">
+        <v>594</v>
+      </c>
+      <c r="D6" t="s">
+        <v>595</v>
+      </c>
+      <c r="E6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C7" t="s">
+        <v>597</v>
+      </c>
+      <c r="D7" t="s">
+        <v>598</v>
+      </c>
+      <c r="E7" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>600</v>
+      </c>
+      <c r="B9" t="s">
+        <v>601</v>
+      </c>
+      <c r="C9" t="s">
+        <v>602</v>
+      </c>
+      <c r="D9" t="s">
+        <v>603</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3A030E-BFDC-437A-B7B4-66B6A130E97D}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>605</v>
+      </c>
+      <c r="B1" t="s">
+        <v>606</v>
+      </c>
+      <c r="C1" t="s">
+        <v>607</v>
+      </c>
+      <c r="D1" t="s">
+        <v>608</v>
+      </c>
+      <c r="E1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B2" t="s">
+        <v>611</v>
+      </c>
+      <c r="C2" t="s">
+        <v>612</v>
+      </c>
+      <c r="D2" t="s">
+        <v>613</v>
+      </c>
+      <c r="E2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C3" t="s">
+        <v>617</v>
+      </c>
+      <c r="D3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E3" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>868</v>
+      </c>
+      <c r="B4" t="s">
+        <v>703</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>621</v>
+      </c>
+      <c r="B5" t="s">
+        <v>622</v>
+      </c>
+      <c r="C5" t="s">
+        <v>623</v>
+      </c>
+      <c r="D5" t="s">
+        <v>624</v>
+      </c>
+      <c r="E5" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B6" t="s">
+        <v>623</v>
+      </c>
+      <c r="C6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D6" t="s">
+        <v>625</v>
+      </c>
+      <c r="E6" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>627</v>
+      </c>
+      <c r="B7" t="s">
+        <v>628</v>
+      </c>
+      <c r="C7" t="s">
+        <v>629</v>
+      </c>
+      <c r="D7" t="s">
+        <v>630</v>
+      </c>
+      <c r="E7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>632</v>
+      </c>
+      <c r="B8" t="s">
+        <v>629</v>
+      </c>
+      <c r="C8" t="s">
+        <v>628</v>
+      </c>
+      <c r="D8" t="s">
+        <v>630</v>
+      </c>
+      <c r="E8" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>633</v>
+      </c>
+      <c r="B9" t="s">
+        <v>634</v>
+      </c>
+      <c r="C9" t="s">
+        <v>635</v>
+      </c>
+      <c r="D9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>718</v>
+      </c>
+      <c r="B10" t="s">
+        <v>635</v>
+      </c>
+      <c r="C10" t="s">
+        <v>634</v>
+      </c>
+      <c r="D10" t="s">
+        <v>636</v>
+      </c>
+      <c r="E10" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" t="s">
+        <v>639</v>
+      </c>
+      <c r="C11" t="s">
+        <v>640</v>
+      </c>
+      <c r="D11" t="s">
+        <v>641</v>
+      </c>
+      <c r="E11" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>638</v>
+      </c>
+      <c r="B12" t="s">
+        <v>639</v>
+      </c>
+      <c r="C12" t="s">
+        <v>640</v>
+      </c>
+      <c r="D12" t="s">
+        <v>641</v>
+      </c>
+      <c r="E12" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>642</v>
+      </c>
+      <c r="B13" t="s">
+        <v>644</v>
+      </c>
+      <c r="C13" t="s">
+        <v>645</v>
+      </c>
+      <c r="D13" t="s">
+        <v>646</v>
+      </c>
+      <c r="E13" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>643</v>
+      </c>
+      <c r="B14" t="s">
+        <v>645</v>
+      </c>
+      <c r="C14" t="s">
+        <v>644</v>
+      </c>
+      <c r="D14" t="s">
+        <v>646</v>
+      </c>
+      <c r="E14" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>647</v>
+      </c>
+      <c r="B15" t="s">
+        <v>648</v>
+      </c>
+      <c r="C15" t="s">
+        <v>649</v>
+      </c>
+      <c r="D15" t="s">
+        <v>650</v>
+      </c>
+      <c r="E15" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>652</v>
+      </c>
+      <c r="B16" t="s">
+        <v>649</v>
+      </c>
+      <c r="C16" t="s">
+        <v>650</v>
+      </c>
+      <c r="D16" t="s">
+        <v>648</v>
+      </c>
+      <c r="E16" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>653</v>
+      </c>
+      <c r="B17" t="s">
+        <v>656</v>
+      </c>
+      <c r="C17" t="s">
+        <v>654</v>
+      </c>
+      <c r="D17" t="s">
+        <v>655</v>
+      </c>
+      <c r="E17" t="s">
+        <v>657</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E301A500-6863-4453-B89E-63F82BD6F98A}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s">
+        <v>659</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C2" t="s">
+        <v>666</v>
+      </c>
+      <c r="D2" t="s">
+        <v>663</v>
+      </c>
+      <c r="E2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B3" t="s">
+        <v>664</v>
+      </c>
+      <c r="C3" t="s">
+        <v>665</v>
+      </c>
+      <c r="D3" t="s">
+        <v>667</v>
+      </c>
+      <c r="E3" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>670</v>
+      </c>
+      <c r="B4" t="s">
+        <v>668</v>
+      </c>
+      <c r="C4">
+        <v>4000</v>
+      </c>
+      <c r="D4" t="s">
+        <v>669</v>
+      </c>
+      <c r="E4" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>671</v>
+      </c>
+      <c r="B5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C5" t="s">
+        <v>673</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="E5" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>675</v>
+      </c>
+      <c r="B6" t="s">
+        <v>676</v>
+      </c>
+      <c r="C6" t="s">
+        <v>677</v>
+      </c>
+      <c r="D6" t="s">
+        <v>679</v>
+      </c>
+      <c r="E6" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>680</v>
+      </c>
+      <c r="B7" t="s">
+        <v>681</v>
+      </c>
+      <c r="C7" t="s">
+        <v>682</v>
+      </c>
+      <c r="D7" t="s">
+        <v>683</v>
+      </c>
+      <c r="E7" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B8" t="s">
+        <v>686</v>
+      </c>
+      <c r="C8" t="s">
+        <v>687</v>
+      </c>
+      <c r="D8" t="s">
+        <v>688</v>
+      </c>
+      <c r="E8" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B9" t="s">
+        <v>689</v>
+      </c>
+      <c r="C9" t="s">
+        <v>682</v>
+      </c>
+      <c r="D9" t="s">
+        <v>683</v>
+      </c>
+      <c r="E9" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>690</v>
+      </c>
+      <c r="B10" t="s">
+        <v>601</v>
+      </c>
+      <c r="C10" t="s">
+        <v>602</v>
+      </c>
+      <c r="D10" t="s">
+        <v>691</v>
+      </c>
+      <c r="E10" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>693</v>
+      </c>
+      <c r="B11" t="s">
+        <v>694</v>
+      </c>
+      <c r="C11" t="s">
+        <v>695</v>
+      </c>
+      <c r="D11" t="s">
+        <v>696</v>
+      </c>
+      <c r="E11" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>698</v>
+      </c>
+      <c r="B12" t="s">
+        <v>869</v>
+      </c>
+      <c r="C12" t="s">
+        <v>870</v>
+      </c>
+      <c r="D12" t="s">
+        <v>871</v>
+      </c>
+      <c r="E12" t="s">
+        <v>699</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D1" r:id="rId1" display="\\omega" xr:uid="{A6F66DDF-44DC-44A3-B421-C2ACB3DABA86}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5BDF8-27D8-4B9B-BEA8-EAE66F52135C}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>701</v>
+      </c>
+      <c r="D1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E1" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="E2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>872</v>
+      </c>
+      <c r="B3" t="s">
+        <v>704</v>
+      </c>
+      <c r="C3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E3" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>702</v>
+      </c>
+      <c r="B4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C4" t="s">
+        <v>270</v>
+      </c>
+      <c r="D4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E4" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>626</v>
+      </c>
+      <c r="B5" t="s">
+        <v>623</v>
+      </c>
+      <c r="C5" t="s">
+        <v>624</v>
+      </c>
+      <c r="D5" t="s">
+        <v>625</v>
+      </c>
+      <c r="E5" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D6" t="s">
+        <v>630</v>
+      </c>
+      <c r="E6" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>713</v>
+      </c>
+      <c r="B7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C7" t="s">
+        <v>628</v>
+      </c>
+      <c r="D7" t="s">
+        <v>630</v>
+      </c>
+      <c r="E7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>714</v>
+      </c>
+      <c r="B8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" t="s">
+        <v>636</v>
+      </c>
+      <c r="E8" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>715</v>
+      </c>
+      <c r="B9" t="s">
+        <v>635</v>
+      </c>
+      <c r="C9" t="s">
+        <v>634</v>
+      </c>
+      <c r="D9" t="s">
+        <v>636</v>
+      </c>
+      <c r="E9" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>716</v>
+      </c>
+      <c r="B10" t="s">
+        <v>719</v>
+      </c>
+      <c r="C10" t="s">
+        <v>495</v>
+      </c>
+      <c r="D10" t="s">
+        <v>720</v>
+      </c>
+      <c r="E10" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>717</v>
+      </c>
+      <c r="B11" t="s">
+        <v>719</v>
+      </c>
+      <c r="C11" t="s">
+        <v>495</v>
+      </c>
+      <c r="D11" t="s">
+        <v>720</v>
+      </c>
+      <c r="E11" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>721</v>
+      </c>
+      <c r="B12" t="s">
+        <v>722</v>
+      </c>
+      <c r="C12" t="s">
+        <v>723</v>
+      </c>
+      <c r="D12" t="s">
+        <v>724</v>
+      </c>
+      <c r="E12" t="s">
+        <v>725</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{3C3C6F99-DCF9-4256-886F-C01CCEEF2611}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A53CF5A-C82B-4A1A-B79E-CD6014286BC3}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C1" t="s">
+        <v>727</v>
+      </c>
+      <c r="D1" t="s">
+        <v>728</v>
+      </c>
+      <c r="E1" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D2" t="s">
+        <v>875</v>
+      </c>
+      <c r="E2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>730</v>
+      </c>
+      <c r="B3" t="s">
+        <v>732</v>
+      </c>
+      <c r="C3" t="s">
+        <v>731</v>
+      </c>
+      <c r="D3" t="s">
+        <v>733</v>
+      </c>
+      <c r="E3" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>730</v>
+      </c>
+      <c r="B4" t="s">
+        <v>735</v>
+      </c>
+      <c r="C4" t="s">
+        <v>731</v>
+      </c>
+      <c r="D4" t="s">
+        <v>733</v>
+      </c>
+      <c r="E4" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>730</v>
+      </c>
+      <c r="B5" t="s">
+        <v>736</v>
+      </c>
+      <c r="C5" t="s">
+        <v>731</v>
+      </c>
+      <c r="D5" t="s">
+        <v>733</v>
+      </c>
+      <c r="E5" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>737</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D6" t="s">
+        <v>738</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>739</v>
+      </c>
+      <c r="B7" t="s">
+        <v>740</v>
+      </c>
+      <c r="C7" t="s">
+        <v>735</v>
+      </c>
+      <c r="D7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>741</v>
+      </c>
+      <c r="B8" t="s">
+        <v>742</v>
+      </c>
+      <c r="C8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>743</v>
+      </c>
+      <c r="E8" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C9" t="s">
+        <v>745</v>
+      </c>
+      <c r="D9" t="s">
+        <v>743</v>
+      </c>
+      <c r="E9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>747</v>
+      </c>
+      <c r="B10" t="s">
+        <v>798</v>
+      </c>
+      <c r="C10" t="s">
+        <v>744</v>
+      </c>
+      <c r="D10" t="s">
+        <v>743</v>
+      </c>
+      <c r="E10" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>748</v>
+      </c>
+      <c r="B11" t="s">
+        <v>743</v>
+      </c>
+      <c r="C11" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" t="s">
+        <v>798</v>
+      </c>
+      <c r="E11" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>749</v>
+      </c>
+      <c r="B12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
+        <v>134</v>
+      </c>
+      <c r="D12" t="s">
+        <v>750</v>
+      </c>
+      <c r="E12" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>754</v>
+      </c>
+      <c r="B13" t="s">
+        <v>752</v>
+      </c>
+      <c r="C13" t="s">
+        <v>753</v>
+      </c>
+      <c r="D13" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>755</v>
+      </c>
+      <c r="B14" t="s">
+        <v>756</v>
+      </c>
+      <c r="C14" t="s">
+        <v>757</v>
+      </c>
+      <c r="D14" t="s">
+        <v>758</v>
+      </c>
+      <c r="E14" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>759</v>
+      </c>
+      <c r="B15" t="s">
+        <v>760</v>
+      </c>
+      <c r="C15" t="s">
+        <v>761</v>
+      </c>
+      <c r="D15" t="s">
+        <v>762</v>
+      </c>
+      <c r="E15" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>764</v>
+      </c>
+      <c r="B16" t="s">
+        <v>757</v>
+      </c>
+      <c r="C16" t="s">
+        <v>756</v>
+      </c>
+      <c r="D16" t="s">
+        <v>765</v>
+      </c>
+      <c r="E16" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>767</v>
+      </c>
+      <c r="B17" t="s">
+        <v>795</v>
+      </c>
+      <c r="C17" t="s">
+        <v>796</v>
+      </c>
+      <c r="D17" t="s">
+        <v>768</v>
+      </c>
+      <c r="E17" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>876</v>
+      </c>
+      <c r="B18" t="s">
+        <v>770</v>
+      </c>
+      <c r="C18" t="s">
+        <v>771</v>
+      </c>
+      <c r="D18" t="s">
+        <v>797</v>
+      </c>
+      <c r="E18" t="s">
+        <v>795</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B7D6DF-E3EA-442B-88C9-26CD6FCC4C27}">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B2" t="s">
+        <v>777</v>
+      </c>
+      <c r="C2" t="s">
+        <v>778</v>
+      </c>
+      <c r="D2" t="s">
+        <v>779</v>
+      </c>
+      <c r="E2" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C3" t="s">
+        <v>781</v>
+      </c>
+      <c r="D3" t="s">
+        <v>782</v>
+      </c>
+      <c r="E3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>748</v>
+      </c>
+      <c r="B4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C4" t="s">
+        <v>800</v>
+      </c>
+      <c r="D4" t="s">
+        <v>791</v>
+      </c>
+      <c r="E4" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>808</v>
+      </c>
+      <c r="B5" t="s">
+        <v>783</v>
+      </c>
+      <c r="C5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" t="s">
+        <v>291</v>
+      </c>
+      <c r="E5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>741</v>
+      </c>
+      <c r="B6" t="s">
+        <v>784</v>
+      </c>
+      <c r="C6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D6" t="s">
+        <v>743</v>
+      </c>
+      <c r="E6" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>785</v>
+      </c>
+      <c r="B7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C7" t="s">
+        <v>787</v>
+      </c>
+      <c r="D7" t="s">
+        <v>788</v>
+      </c>
+      <c r="E7" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>791</v>
+      </c>
+      <c r="D8" t="s">
+        <v>792</v>
+      </c>
+      <c r="E8" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>794</v>
+      </c>
+      <c r="B9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C9" t="s">
+        <v>784</v>
+      </c>
+      <c r="D9" t="s">
+        <v>743</v>
+      </c>
+      <c r="E9" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>794</v>
+      </c>
+      <c r="B10" t="s">
+        <v>787</v>
+      </c>
+      <c r="C10" t="s">
+        <v>784</v>
+      </c>
+      <c r="D10" t="s">
+        <v>743</v>
+      </c>
+      <c r="E10" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>747</v>
+      </c>
+      <c r="B11" t="s">
+        <v>798</v>
+      </c>
+      <c r="C11" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" t="s">
+        <v>743</v>
+      </c>
+      <c r="E11" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>748</v>
+      </c>
+      <c r="B12" t="s">
+        <v>743</v>
+      </c>
+      <c r="C12" t="s">
+        <v>744</v>
+      </c>
+      <c r="D12" t="s">
+        <v>798</v>
+      </c>
+      <c r="E12" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>749</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>134</v>
+      </c>
+      <c r="D13" t="s">
+        <v>750</v>
+      </c>
+      <c r="E13" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>767</v>
+      </c>
+      <c r="B14" t="s">
+        <v>795</v>
+      </c>
+      <c r="C14" t="s">
+        <v>796</v>
+      </c>
+      <c r="D14" t="s">
+        <v>768</v>
+      </c>
+      <c r="E14" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>876</v>
+      </c>
+      <c r="B15" t="s">
+        <v>770</v>
+      </c>
+      <c r="C15" t="s">
+        <v>878</v>
+      </c>
+      <c r="D15" t="s">
+        <v>797</v>
+      </c>
+      <c r="E15" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>759</v>
+      </c>
+      <c r="B16" t="s">
+        <v>760</v>
+      </c>
+      <c r="C16" t="s">
+        <v>761</v>
+      </c>
+      <c r="D16" t="s">
+        <v>762</v>
+      </c>
+      <c r="E16" t="s">
+        <v>763</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613919D5-98DA-4E9C-9276-103BEB2B8675}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B1" t="s">
+        <v>773</v>
+      </c>
+      <c r="C1" t="s">
+        <v>774</v>
+      </c>
+      <c r="D1" t="s">
+        <v>775</v>
+      </c>
+      <c r="E1" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>802</v>
+      </c>
+      <c r="B2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E2" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>805</v>
+      </c>
+      <c r="B3" t="s">
+        <v>806</v>
+      </c>
+      <c r="C3" t="s">
+        <v>728</v>
+      </c>
+      <c r="D3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>804</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>781</v>
+      </c>
+      <c r="D4" t="s">
+        <v>782</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>748</v>
+      </c>
+      <c r="B5" t="s">
+        <v>807</v>
+      </c>
+      <c r="C5" t="s">
+        <v>800</v>
+      </c>
+      <c r="D5" t="s">
+        <v>791</v>
+      </c>
+      <c r="E5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>815</v>
+      </c>
+      <c r="B6" t="s">
+        <v>732</v>
+      </c>
+      <c r="C6" t="s">
+        <v>731</v>
+      </c>
+      <c r="D6" t="s">
+        <v>733</v>
+      </c>
+      <c r="E6" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>815</v>
+      </c>
+      <c r="B7" t="s">
+        <v>735</v>
+      </c>
+      <c r="C7" t="s">
+        <v>731</v>
+      </c>
+      <c r="D7" t="s">
+        <v>733</v>
+      </c>
+      <c r="E7" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>815</v>
+      </c>
+      <c r="B8" t="s">
+        <v>736</v>
+      </c>
+      <c r="C8" t="s">
+        <v>731</v>
+      </c>
+      <c r="D8" t="s">
+        <v>733</v>
+      </c>
+      <c r="E8" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B9" t="s">
+        <v>784</v>
+      </c>
+      <c r="C9" t="s">
+        <v>809</v>
+      </c>
+      <c r="D9" t="s">
+        <v>743</v>
+      </c>
+      <c r="E9" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>808</v>
+      </c>
+      <c r="B10" t="s">
+        <v>783</v>
+      </c>
+      <c r="C10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>747</v>
+      </c>
+      <c r="B11" t="s">
+        <v>798</v>
+      </c>
+      <c r="C11" t="s">
+        <v>744</v>
+      </c>
+      <c r="D11" t="s">
+        <v>743</v>
+      </c>
+      <c r="E11" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>748</v>
+      </c>
+      <c r="B12" t="s">
+        <v>743</v>
+      </c>
+      <c r="C12" t="s">
+        <v>744</v>
+      </c>
+      <c r="D12" t="s">
+        <v>798</v>
+      </c>
+      <c r="E12" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>810</v>
+      </c>
+      <c r="B13" t="s">
+        <v>811</v>
+      </c>
+      <c r="C13" t="s">
+        <v>812</v>
+      </c>
+      <c r="D13" t="s">
+        <v>813</v>
+      </c>
+      <c r="E13" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>749</v>
+      </c>
+      <c r="B14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D14" t="s">
+        <v>750</v>
+      </c>
+      <c r="E14" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>767</v>
+      </c>
+      <c r="B15" t="s">
+        <v>795</v>
+      </c>
+      <c r="C15" t="s">
+        <v>796</v>
+      </c>
+      <c r="D15" t="s">
+        <v>768</v>
+      </c>
+      <c r="E15" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>876</v>
+      </c>
+      <c r="B16" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" t="s">
+        <v>878</v>
+      </c>
+      <c r="D16" t="s">
+        <v>797</v>
+      </c>
+      <c r="E16" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>759</v>
+      </c>
+      <c r="B17" t="s">
+        <v>760</v>
+      </c>
+      <c r="C17" t="s">
+        <v>761</v>
+      </c>
+      <c r="D17" t="s">
+        <v>762</v>
+      </c>
+      <c r="E17" t="s">
+        <v>763</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE91C49D-AC90-484D-977A-FE1BA9A7FAF7}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="35.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B1" t="s">
+        <v>879</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="D1" t="s">
+        <v>818</v>
+      </c>
+      <c r="E1" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C2" t="s">
+        <v>822</v>
+      </c>
+      <c r="D2" t="s">
+        <v>823</v>
+      </c>
+      <c r="E2" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>825</v>
+      </c>
+      <c r="B3" t="s">
+        <v>819</v>
+      </c>
+      <c r="C3" t="s">
+        <v>818</v>
+      </c>
+      <c r="D3" t="s">
+        <v>879</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>827</v>
+      </c>
+      <c r="B4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C4" t="s">
+        <v>881</v>
+      </c>
+      <c r="D4" t="s">
+        <v>882</v>
+      </c>
+      <c r="E4" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>886</v>
+      </c>
+      <c r="B5" t="s">
+        <v>881</v>
+      </c>
+      <c r="C5" t="s">
+        <v>880</v>
+      </c>
+      <c r="D5" t="s">
+        <v>882</v>
+      </c>
+      <c r="E5" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>826</v>
+      </c>
+      <c r="B6" t="s">
+        <v>884</v>
+      </c>
+      <c r="C6" t="s">
+        <v>828</v>
+      </c>
+      <c r="D6" t="s">
+        <v>885</v>
+      </c>
+      <c r="E6" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C7" t="s">
+        <v>817</v>
+      </c>
+      <c r="D7" t="s">
+        <v>776</v>
+      </c>
+      <c r="E7" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>832</v>
+      </c>
+      <c r="B8" t="s">
+        <v>817</v>
+      </c>
+      <c r="C8" t="s">
+        <v>830</v>
+      </c>
+      <c r="D8" t="s">
+        <v>776</v>
+      </c>
+      <c r="E8" t="s">
+        <v>831</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C1" r:id="rId1" display="\\frac'\\Delta s}{\\Delta m}" xr:uid="{9EBE9598-93DE-44B1-9E12-35D0695E2A1D}"/>
+    <hyperlink ref="E3" r:id="rId2" display="\\frac'\\Delta s}{\\Delta m}" xr:uid="{603A108F-9A9B-4540-BB60-AF31490918AF}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A72E7E-7D71-4D59-A32C-F045310BF716}">
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3847,2245 +8551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF4AF2B7-091E-41FA-A36B-72547CA4D295}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>536</v>
-      </c>
-      <c r="B1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>537</v>
-      </c>
-      <c r="B2" t="s">
-        <v>538</v>
-      </c>
-      <c r="C2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E2" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B3" t="s">
-        <v>494</v>
-      </c>
-      <c r="C3" t="s">
-        <v>495</v>
-      </c>
-      <c r="D3" t="s">
-        <v>496</v>
-      </c>
-      <c r="E3" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>541</v>
-      </c>
-      <c r="B4" t="s">
-        <v>542</v>
-      </c>
-      <c r="C4" t="s">
-        <v>543</v>
-      </c>
-      <c r="D4" t="s">
-        <v>517</v>
-      </c>
-      <c r="E4" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>550</v>
-      </c>
-      <c r="B5" t="s">
-        <v>554</v>
-      </c>
-      <c r="C5" t="s">
-        <v>547</v>
-      </c>
-      <c r="D5" t="s">
-        <v>545</v>
-      </c>
-      <c r="E5" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>867</v>
-      </c>
-      <c r="B6" t="s">
-        <v>547</v>
-      </c>
-      <c r="C6" t="s">
-        <v>555</v>
-      </c>
-      <c r="D6" t="s">
-        <v>548</v>
-      </c>
-      <c r="E6" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>551</v>
-      </c>
-      <c r="B7" t="s">
-        <v>552</v>
-      </c>
-      <c r="C7" t="s">
-        <v>553</v>
-      </c>
-      <c r="D7" t="s">
-        <v>554</v>
-      </c>
-      <c r="E7" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="B8" t="s">
-        <v>557</v>
-      </c>
-      <c r="C8" t="s">
-        <v>558</v>
-      </c>
-      <c r="D8" t="s">
-        <v>559</v>
-      </c>
-      <c r="E8" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>561</v>
-      </c>
-      <c r="B9" t="s">
-        <v>516</v>
-      </c>
-      <c r="C9" t="s">
-        <v>562</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>524</v>
-      </c>
-      <c r="B10" t="s">
-        <v>563</v>
-      </c>
-      <c r="C10" t="s">
-        <v>564</v>
-      </c>
-      <c r="D10" t="s">
-        <v>521</v>
-      </c>
-      <c r="E10" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>525</v>
-      </c>
-      <c r="B11" t="s">
-        <v>565</v>
-      </c>
-      <c r="C11" t="s">
-        <v>521</v>
-      </c>
-      <c r="D11" t="s">
-        <v>566</v>
-      </c>
-      <c r="E11" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>526</v>
-      </c>
-      <c r="B12" t="s">
-        <v>566</v>
-      </c>
-      <c r="C12" t="s">
-        <v>531</v>
-      </c>
-      <c r="D12" t="s">
-        <v>522</v>
-      </c>
-      <c r="E12" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>567</v>
-      </c>
-      <c r="B13" t="s">
-        <v>568</v>
-      </c>
-      <c r="C13" t="s">
-        <v>569</v>
-      </c>
-      <c r="D13" t="s">
-        <v>570</v>
-      </c>
-      <c r="E13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>571</v>
-      </c>
-      <c r="B14" t="s">
-        <v>572</v>
-      </c>
-      <c r="C14" t="s">
-        <v>573</v>
-      </c>
-      <c r="D14" t="s">
-        <v>575</v>
-      </c>
-      <c r="E14" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>585</v>
-      </c>
-      <c r="B15" t="s">
-        <v>586</v>
-      </c>
-      <c r="C15" t="s">
-        <v>587</v>
-      </c>
-      <c r="D15" t="s">
-        <v>588</v>
-      </c>
-      <c r="E15" t="s">
-        <v>589</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A8" r:id="rId1" xr:uid="{9AED4FB5-E535-47E0-B49B-11BCE2A9FA4A}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD96C3AE-00CF-4B4E-AD9B-52BC273DAF9D}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B1" t="s">
-        <v>577</v>
-      </c>
-      <c r="C1" t="s">
-        <v>578</v>
-      </c>
-      <c r="D1" t="s">
-        <v>579</v>
-      </c>
-      <c r="E1" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B2" t="s">
-        <v>582</v>
-      </c>
-      <c r="C2" t="s">
-        <v>583</v>
-      </c>
-      <c r="D2" t="s">
-        <v>584</v>
-      </c>
-      <c r="E2" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>585</v>
-      </c>
-      <c r="B3" t="s">
-        <v>586</v>
-      </c>
-      <c r="C3" t="s">
-        <v>587</v>
-      </c>
-      <c r="D3" t="s">
-        <v>588</v>
-      </c>
-      <c r="E3" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C4" t="s">
-        <v>223</v>
-      </c>
-      <c r="D4" t="s">
-        <v>226</v>
-      </c>
-      <c r="E4" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B5" t="s">
-        <v>223</v>
-      </c>
-      <c r="C5" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" t="s">
-        <v>224</v>
-      </c>
-      <c r="E5" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>592</v>
-      </c>
-      <c r="B6" t="s">
-        <v>593</v>
-      </c>
-      <c r="C6" t="s">
-        <v>594</v>
-      </c>
-      <c r="D6" t="s">
-        <v>595</v>
-      </c>
-      <c r="E6" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>227</v>
-      </c>
-      <c r="B7" t="s">
-        <v>596</v>
-      </c>
-      <c r="C7" t="s">
-        <v>597</v>
-      </c>
-      <c r="D7" t="s">
-        <v>598</v>
-      </c>
-      <c r="E7" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" t="s">
-        <v>228</v>
-      </c>
-      <c r="C8" t="s">
-        <v>229</v>
-      </c>
-      <c r="D8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E8" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>600</v>
-      </c>
-      <c r="B9" t="s">
-        <v>601</v>
-      </c>
-      <c r="C9" t="s">
-        <v>602</v>
-      </c>
-      <c r="D9" t="s">
-        <v>603</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>604</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3A030E-BFDC-437A-B7B4-66B6A130E97D}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>605</v>
-      </c>
-      <c r="B1" t="s">
-        <v>606</v>
-      </c>
-      <c r="C1" t="s">
-        <v>607</v>
-      </c>
-      <c r="D1" t="s">
-        <v>608</v>
-      </c>
-      <c r="E1" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>610</v>
-      </c>
-      <c r="B2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D2" t="s">
-        <v>613</v>
-      </c>
-      <c r="E2" t="s">
-        <v>614</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>615</v>
-      </c>
-      <c r="B3" t="s">
-        <v>616</v>
-      </c>
-      <c r="C3" t="s">
-        <v>617</v>
-      </c>
-      <c r="D3" t="s">
-        <v>618</v>
-      </c>
-      <c r="E3" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>868</v>
-      </c>
-      <c r="B4" t="s">
-        <v>703</v>
-      </c>
-      <c r="C4" t="s">
-        <v>133</v>
-      </c>
-      <c r="D4" t="s">
-        <v>620</v>
-      </c>
-      <c r="E4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>621</v>
-      </c>
-      <c r="B5" t="s">
-        <v>622</v>
-      </c>
-      <c r="C5" t="s">
-        <v>623</v>
-      </c>
-      <c r="D5" t="s">
-        <v>624</v>
-      </c>
-      <c r="E5" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>626</v>
-      </c>
-      <c r="B6" t="s">
-        <v>623</v>
-      </c>
-      <c r="C6" t="s">
-        <v>624</v>
-      </c>
-      <c r="D6" t="s">
-        <v>625</v>
-      </c>
-      <c r="E6" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>627</v>
-      </c>
-      <c r="B7" t="s">
-        <v>628</v>
-      </c>
-      <c r="C7" t="s">
-        <v>629</v>
-      </c>
-      <c r="D7" t="s">
-        <v>630</v>
-      </c>
-      <c r="E7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>632</v>
-      </c>
-      <c r="B8" t="s">
-        <v>629</v>
-      </c>
-      <c r="C8" t="s">
-        <v>628</v>
-      </c>
-      <c r="D8" t="s">
-        <v>630</v>
-      </c>
-      <c r="E8" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>633</v>
-      </c>
-      <c r="B9" t="s">
-        <v>634</v>
-      </c>
-      <c r="C9" t="s">
-        <v>635</v>
-      </c>
-      <c r="D9" t="s">
-        <v>636</v>
-      </c>
-      <c r="E9" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>718</v>
-      </c>
-      <c r="B10" t="s">
-        <v>635</v>
-      </c>
-      <c r="C10" t="s">
-        <v>634</v>
-      </c>
-      <c r="D10" t="s">
-        <v>636</v>
-      </c>
-      <c r="E10" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>637</v>
-      </c>
-      <c r="B11" t="s">
-        <v>639</v>
-      </c>
-      <c r="C11" t="s">
-        <v>640</v>
-      </c>
-      <c r="D11" t="s">
-        <v>641</v>
-      </c>
-      <c r="E11" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>638</v>
-      </c>
-      <c r="B12" t="s">
-        <v>639</v>
-      </c>
-      <c r="C12" t="s">
-        <v>640</v>
-      </c>
-      <c r="D12" t="s">
-        <v>641</v>
-      </c>
-      <c r="E12" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>642</v>
-      </c>
-      <c r="B13" t="s">
-        <v>644</v>
-      </c>
-      <c r="C13" t="s">
-        <v>645</v>
-      </c>
-      <c r="D13" t="s">
-        <v>646</v>
-      </c>
-      <c r="E13" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>643</v>
-      </c>
-      <c r="B14" t="s">
-        <v>645</v>
-      </c>
-      <c r="C14" t="s">
-        <v>644</v>
-      </c>
-      <c r="D14" t="s">
-        <v>646</v>
-      </c>
-      <c r="E14" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>647</v>
-      </c>
-      <c r="B15" t="s">
-        <v>648</v>
-      </c>
-      <c r="C15" t="s">
-        <v>649</v>
-      </c>
-      <c r="D15" t="s">
-        <v>650</v>
-      </c>
-      <c r="E15" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>652</v>
-      </c>
-      <c r="B16" t="s">
-        <v>649</v>
-      </c>
-      <c r="C16" t="s">
-        <v>650</v>
-      </c>
-      <c r="D16" t="s">
-        <v>648</v>
-      </c>
-      <c r="E16" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>653</v>
-      </c>
-      <c r="B17" t="s">
-        <v>656</v>
-      </c>
-      <c r="C17" t="s">
-        <v>654</v>
-      </c>
-      <c r="D17" t="s">
-        <v>655</v>
-      </c>
-      <c r="E17" t="s">
-        <v>657</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E301A500-6863-4453-B89E-63F82BD6F98A}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>658</v>
-      </c>
-      <c r="B1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" t="s">
-        <v>659</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>661</v>
-      </c>
-      <c r="B2" t="s">
-        <v>662</v>
-      </c>
-      <c r="C2" t="s">
-        <v>666</v>
-      </c>
-      <c r="D2" t="s">
-        <v>663</v>
-      </c>
-      <c r="E2" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>661</v>
-      </c>
-      <c r="B3" t="s">
-        <v>664</v>
-      </c>
-      <c r="C3" t="s">
-        <v>665</v>
-      </c>
-      <c r="D3" t="s">
-        <v>667</v>
-      </c>
-      <c r="E3" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>670</v>
-      </c>
-      <c r="B4" t="s">
-        <v>668</v>
-      </c>
-      <c r="C4">
-        <v>4000</v>
-      </c>
-      <c r="D4" t="s">
-        <v>669</v>
-      </c>
-      <c r="E4" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>671</v>
-      </c>
-      <c r="B5" t="s">
-        <v>672</v>
-      </c>
-      <c r="C5" t="s">
-        <v>673</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="E5" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>675</v>
-      </c>
-      <c r="B6" t="s">
-        <v>676</v>
-      </c>
-      <c r="C6" t="s">
-        <v>677</v>
-      </c>
-      <c r="D6" t="s">
-        <v>679</v>
-      </c>
-      <c r="E6" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>680</v>
-      </c>
-      <c r="B7" t="s">
-        <v>681</v>
-      </c>
-      <c r="C7" t="s">
-        <v>682</v>
-      </c>
-      <c r="D7" t="s">
-        <v>683</v>
-      </c>
-      <c r="E7" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>685</v>
-      </c>
-      <c r="B8" t="s">
-        <v>686</v>
-      </c>
-      <c r="C8" t="s">
-        <v>687</v>
-      </c>
-      <c r="D8" t="s">
-        <v>688</v>
-      </c>
-      <c r="E8" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>680</v>
-      </c>
-      <c r="B9" t="s">
-        <v>689</v>
-      </c>
-      <c r="C9" t="s">
-        <v>682</v>
-      </c>
-      <c r="D9" t="s">
-        <v>683</v>
-      </c>
-      <c r="E9" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>690</v>
-      </c>
-      <c r="B10" t="s">
-        <v>601</v>
-      </c>
-      <c r="C10" t="s">
-        <v>602</v>
-      </c>
-      <c r="D10" t="s">
-        <v>691</v>
-      </c>
-      <c r="E10" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>693</v>
-      </c>
-      <c r="B11" t="s">
-        <v>694</v>
-      </c>
-      <c r="C11" t="s">
-        <v>695</v>
-      </c>
-      <c r="D11" t="s">
-        <v>696</v>
-      </c>
-      <c r="E11" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>698</v>
-      </c>
-      <c r="B12" t="s">
-        <v>869</v>
-      </c>
-      <c r="C12" t="s">
-        <v>870</v>
-      </c>
-      <c r="D12" t="s">
-        <v>871</v>
-      </c>
-      <c r="E12" t="s">
-        <v>699</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D1" r:id="rId1" display="\\omega" xr:uid="{A6F66DDF-44DC-44A3-B421-C2ACB3DABA86}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BB5BDF8-27D8-4B9B-BEA8-EAE66F52135C}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>706</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>701</v>
-      </c>
-      <c r="D1" t="s">
-        <v>634</v>
-      </c>
-      <c r="E1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>705</v>
-      </c>
-      <c r="B2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="E2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>872</v>
-      </c>
-      <c r="B3" t="s">
-        <v>704</v>
-      </c>
-      <c r="C3" t="s">
-        <v>707</v>
-      </c>
-      <c r="D3" t="s">
-        <v>708</v>
-      </c>
-      <c r="E3" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>702</v>
-      </c>
-      <c r="B4" t="s">
-        <v>269</v>
-      </c>
-      <c r="C4" t="s">
-        <v>270</v>
-      </c>
-      <c r="D4" t="s">
-        <v>710</v>
-      </c>
-      <c r="E4" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>626</v>
-      </c>
-      <c r="B5" t="s">
-        <v>623</v>
-      </c>
-      <c r="C5" t="s">
-        <v>624</v>
-      </c>
-      <c r="D5" t="s">
-        <v>625</v>
-      </c>
-      <c r="E5" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>712</v>
-      </c>
-      <c r="B6" t="s">
-        <v>628</v>
-      </c>
-      <c r="C6" t="s">
-        <v>629</v>
-      </c>
-      <c r="D6" t="s">
-        <v>630</v>
-      </c>
-      <c r="E6" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>713</v>
-      </c>
-      <c r="B7" t="s">
-        <v>629</v>
-      </c>
-      <c r="C7" t="s">
-        <v>628</v>
-      </c>
-      <c r="D7" t="s">
-        <v>630</v>
-      </c>
-      <c r="E7" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>714</v>
-      </c>
-      <c r="B8" t="s">
-        <v>634</v>
-      </c>
-      <c r="C8" t="s">
-        <v>635</v>
-      </c>
-      <c r="D8" t="s">
-        <v>636</v>
-      </c>
-      <c r="E8" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>715</v>
-      </c>
-      <c r="B9" t="s">
-        <v>635</v>
-      </c>
-      <c r="C9" t="s">
-        <v>634</v>
-      </c>
-      <c r="D9" t="s">
-        <v>636</v>
-      </c>
-      <c r="E9" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>716</v>
-      </c>
-      <c r="B10" t="s">
-        <v>719</v>
-      </c>
-      <c r="C10" t="s">
-        <v>495</v>
-      </c>
-      <c r="D10" t="s">
-        <v>720</v>
-      </c>
-      <c r="E10" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>717</v>
-      </c>
-      <c r="B11" t="s">
-        <v>719</v>
-      </c>
-      <c r="C11" t="s">
-        <v>495</v>
-      </c>
-      <c r="D11" t="s">
-        <v>720</v>
-      </c>
-      <c r="E11" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>721</v>
-      </c>
-      <c r="B12" t="s">
-        <v>722</v>
-      </c>
-      <c r="C12" t="s">
-        <v>723</v>
-      </c>
-      <c r="D12" t="s">
-        <v>724</v>
-      </c>
-      <c r="E12" t="s">
-        <v>725</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{3C3C6F99-DCF9-4256-886F-C01CCEEF2611}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A53CF5A-C82B-4A1A-B79E-CD6014286BC3}">
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>793</v>
-      </c>
-      <c r="B1" t="s">
-        <v>726</v>
-      </c>
-      <c r="C1" t="s">
-        <v>727</v>
-      </c>
-      <c r="D1" t="s">
-        <v>728</v>
-      </c>
-      <c r="E1" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>793</v>
-      </c>
-      <c r="B2" t="s">
-        <v>873</v>
-      </c>
-      <c r="C2" t="s">
-        <v>874</v>
-      </c>
-      <c r="D2" t="s">
-        <v>875</v>
-      </c>
-      <c r="E2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>730</v>
-      </c>
-      <c r="B3" t="s">
-        <v>732</v>
-      </c>
-      <c r="C3" t="s">
-        <v>731</v>
-      </c>
-      <c r="D3" t="s">
-        <v>733</v>
-      </c>
-      <c r="E3" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>730</v>
-      </c>
-      <c r="B4" t="s">
-        <v>735</v>
-      </c>
-      <c r="C4" t="s">
-        <v>731</v>
-      </c>
-      <c r="D4" t="s">
-        <v>733</v>
-      </c>
-      <c r="E4" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>730</v>
-      </c>
-      <c r="B5" t="s">
-        <v>736</v>
-      </c>
-      <c r="C5" t="s">
-        <v>731</v>
-      </c>
-      <c r="D5" t="s">
-        <v>733</v>
-      </c>
-      <c r="E5" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>737</v>
-      </c>
-      <c r="B6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" t="s">
-        <v>738</v>
-      </c>
-      <c r="E6" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>739</v>
-      </c>
-      <c r="B7" t="s">
-        <v>740</v>
-      </c>
-      <c r="C7" t="s">
-        <v>735</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>741</v>
-      </c>
-      <c r="B8" t="s">
-        <v>742</v>
-      </c>
-      <c r="C8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E8" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>741</v>
-      </c>
-      <c r="B9" t="s">
-        <v>744</v>
-      </c>
-      <c r="C9" t="s">
-        <v>745</v>
-      </c>
-      <c r="D9" t="s">
-        <v>743</v>
-      </c>
-      <c r="E9" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>747</v>
-      </c>
-      <c r="B10" t="s">
-        <v>798</v>
-      </c>
-      <c r="C10" t="s">
-        <v>744</v>
-      </c>
-      <c r="D10" t="s">
-        <v>743</v>
-      </c>
-      <c r="E10" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>748</v>
-      </c>
-      <c r="B11" t="s">
-        <v>743</v>
-      </c>
-      <c r="C11" t="s">
-        <v>744</v>
-      </c>
-      <c r="D11" t="s">
-        <v>798</v>
-      </c>
-      <c r="E11" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>749</v>
-      </c>
-      <c r="B12" t="s">
-        <v>133</v>
-      </c>
-      <c r="C12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" t="s">
-        <v>750</v>
-      </c>
-      <c r="E12" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>754</v>
-      </c>
-      <c r="B13" t="s">
-        <v>752</v>
-      </c>
-      <c r="C13" t="s">
-        <v>753</v>
-      </c>
-      <c r="D13" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>755</v>
-      </c>
-      <c r="B14" t="s">
-        <v>756</v>
-      </c>
-      <c r="C14" t="s">
-        <v>757</v>
-      </c>
-      <c r="D14" t="s">
-        <v>758</v>
-      </c>
-      <c r="E14" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>759</v>
-      </c>
-      <c r="B15" t="s">
-        <v>760</v>
-      </c>
-      <c r="C15" t="s">
-        <v>761</v>
-      </c>
-      <c r="D15" t="s">
-        <v>762</v>
-      </c>
-      <c r="E15" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>764</v>
-      </c>
-      <c r="B16" t="s">
-        <v>757</v>
-      </c>
-      <c r="C16" t="s">
-        <v>756</v>
-      </c>
-      <c r="D16" t="s">
-        <v>765</v>
-      </c>
-      <c r="E16" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>767</v>
-      </c>
-      <c r="B17" t="s">
-        <v>795</v>
-      </c>
-      <c r="C17" t="s">
-        <v>796</v>
-      </c>
-      <c r="D17" t="s">
-        <v>768</v>
-      </c>
-      <c r="E17" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>876</v>
-      </c>
-      <c r="B18" t="s">
-        <v>770</v>
-      </c>
-      <c r="C18" t="s">
-        <v>771</v>
-      </c>
-      <c r="D18" t="s">
-        <v>797</v>
-      </c>
-      <c r="E18" t="s">
-        <v>795</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3B7D6DF-E3EA-442B-88C9-26CD6FCC4C27}">
-  <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>772</v>
-      </c>
-      <c r="B1" t="s">
-        <v>773</v>
-      </c>
-      <c r="C1" t="s">
-        <v>774</v>
-      </c>
-      <c r="D1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>877</v>
-      </c>
-      <c r="B2" t="s">
-        <v>777</v>
-      </c>
-      <c r="C2" t="s">
-        <v>778</v>
-      </c>
-      <c r="D2" t="s">
-        <v>779</v>
-      </c>
-      <c r="E2" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" t="s">
-        <v>246</v>
-      </c>
-      <c r="C3" t="s">
-        <v>781</v>
-      </c>
-      <c r="D3" t="s">
-        <v>782</v>
-      </c>
-      <c r="E3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>748</v>
-      </c>
-      <c r="B4" t="s">
-        <v>799</v>
-      </c>
-      <c r="C4" t="s">
-        <v>800</v>
-      </c>
-      <c r="D4" t="s">
-        <v>791</v>
-      </c>
-      <c r="E4" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>808</v>
-      </c>
-      <c r="B5" t="s">
-        <v>783</v>
-      </c>
-      <c r="C5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>741</v>
-      </c>
-      <c r="B6" t="s">
-        <v>784</v>
-      </c>
-      <c r="C6" t="s">
-        <v>744</v>
-      </c>
-      <c r="D6" t="s">
-        <v>743</v>
-      </c>
-      <c r="E6" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>785</v>
-      </c>
-      <c r="B7" t="s">
-        <v>786</v>
-      </c>
-      <c r="C7" t="s">
-        <v>787</v>
-      </c>
-      <c r="D7" t="s">
-        <v>788</v>
-      </c>
-      <c r="E7" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>790</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8" t="s">
-        <v>791</v>
-      </c>
-      <c r="D8" t="s">
-        <v>792</v>
-      </c>
-      <c r="E8" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>794</v>
-      </c>
-      <c r="B9" t="s">
-        <v>744</v>
-      </c>
-      <c r="C9" t="s">
-        <v>784</v>
-      </c>
-      <c r="D9" t="s">
-        <v>743</v>
-      </c>
-      <c r="E9" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>794</v>
-      </c>
-      <c r="B10" t="s">
-        <v>787</v>
-      </c>
-      <c r="C10" t="s">
-        <v>784</v>
-      </c>
-      <c r="D10" t="s">
-        <v>743</v>
-      </c>
-      <c r="E10" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>747</v>
-      </c>
-      <c r="B11" t="s">
-        <v>798</v>
-      </c>
-      <c r="C11" t="s">
-        <v>744</v>
-      </c>
-      <c r="D11" t="s">
-        <v>743</v>
-      </c>
-      <c r="E11" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>748</v>
-      </c>
-      <c r="B12" t="s">
-        <v>743</v>
-      </c>
-      <c r="C12" t="s">
-        <v>744</v>
-      </c>
-      <c r="D12" t="s">
-        <v>798</v>
-      </c>
-      <c r="E12" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>749</v>
-      </c>
-      <c r="B13" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" t="s">
-        <v>134</v>
-      </c>
-      <c r="D13" t="s">
-        <v>750</v>
-      </c>
-      <c r="E13" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>767</v>
-      </c>
-      <c r="B14" t="s">
-        <v>795</v>
-      </c>
-      <c r="C14" t="s">
-        <v>796</v>
-      </c>
-      <c r="D14" t="s">
-        <v>768</v>
-      </c>
-      <c r="E14" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>876</v>
-      </c>
-      <c r="B15" t="s">
-        <v>770</v>
-      </c>
-      <c r="C15" t="s">
-        <v>878</v>
-      </c>
-      <c r="D15" t="s">
-        <v>797</v>
-      </c>
-      <c r="E15" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>759</v>
-      </c>
-      <c r="B16" t="s">
-        <v>760</v>
-      </c>
-      <c r="C16" t="s">
-        <v>761</v>
-      </c>
-      <c r="D16" t="s">
-        <v>762</v>
-      </c>
-      <c r="E16" t="s">
-        <v>763</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613919D5-98DA-4E9C-9276-103BEB2B8675}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>772</v>
-      </c>
-      <c r="B1" t="s">
-        <v>773</v>
-      </c>
-      <c r="C1" t="s">
-        <v>774</v>
-      </c>
-      <c r="D1" t="s">
-        <v>775</v>
-      </c>
-      <c r="E1" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>802</v>
-      </c>
-      <c r="B2" t="s">
-        <v>773</v>
-      </c>
-      <c r="C2" t="s">
-        <v>774</v>
-      </c>
-      <c r="D2" t="s">
-        <v>775</v>
-      </c>
-      <c r="E2" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>805</v>
-      </c>
-      <c r="B3" t="s">
-        <v>806</v>
-      </c>
-      <c r="C3" t="s">
-        <v>728</v>
-      </c>
-      <c r="D3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>804</v>
-      </c>
-      <c r="B4" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" t="s">
-        <v>781</v>
-      </c>
-      <c r="D4" t="s">
-        <v>782</v>
-      </c>
-      <c r="E4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>748</v>
-      </c>
-      <c r="B5" t="s">
-        <v>807</v>
-      </c>
-      <c r="C5" t="s">
-        <v>800</v>
-      </c>
-      <c r="D5" t="s">
-        <v>791</v>
-      </c>
-      <c r="E5" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>815</v>
-      </c>
-      <c r="B6" t="s">
-        <v>732</v>
-      </c>
-      <c r="C6" t="s">
-        <v>731</v>
-      </c>
-      <c r="D6" t="s">
-        <v>733</v>
-      </c>
-      <c r="E6" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>815</v>
-      </c>
-      <c r="B7" t="s">
-        <v>735</v>
-      </c>
-      <c r="C7" t="s">
-        <v>731</v>
-      </c>
-      <c r="D7" t="s">
-        <v>733</v>
-      </c>
-      <c r="E7" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>815</v>
-      </c>
-      <c r="B8" t="s">
-        <v>736</v>
-      </c>
-      <c r="C8" t="s">
-        <v>731</v>
-      </c>
-      <c r="D8" t="s">
-        <v>733</v>
-      </c>
-      <c r="E8" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>741</v>
-      </c>
-      <c r="B9" t="s">
-        <v>784</v>
-      </c>
-      <c r="C9" t="s">
-        <v>809</v>
-      </c>
-      <c r="D9" t="s">
-        <v>743</v>
-      </c>
-      <c r="E9" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>808</v>
-      </c>
-      <c r="B10" t="s">
-        <v>783</v>
-      </c>
-      <c r="C10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>747</v>
-      </c>
-      <c r="B11" t="s">
-        <v>798</v>
-      </c>
-      <c r="C11" t="s">
-        <v>744</v>
-      </c>
-      <c r="D11" t="s">
-        <v>743</v>
-      </c>
-      <c r="E11" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>748</v>
-      </c>
-      <c r="B12" t="s">
-        <v>743</v>
-      </c>
-      <c r="C12" t="s">
-        <v>744</v>
-      </c>
-      <c r="D12" t="s">
-        <v>798</v>
-      </c>
-      <c r="E12" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>810</v>
-      </c>
-      <c r="B13" t="s">
-        <v>811</v>
-      </c>
-      <c r="C13" t="s">
-        <v>812</v>
-      </c>
-      <c r="D13" t="s">
-        <v>813</v>
-      </c>
-      <c r="E13" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>749</v>
-      </c>
-      <c r="B14" t="s">
-        <v>133</v>
-      </c>
-      <c r="C14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D14" t="s">
-        <v>750</v>
-      </c>
-      <c r="E14" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>767</v>
-      </c>
-      <c r="B15" t="s">
-        <v>795</v>
-      </c>
-      <c r="C15" t="s">
-        <v>796</v>
-      </c>
-      <c r="D15" t="s">
-        <v>768</v>
-      </c>
-      <c r="E15" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>876</v>
-      </c>
-      <c r="B16" t="s">
-        <v>770</v>
-      </c>
-      <c r="C16" t="s">
-        <v>878</v>
-      </c>
-      <c r="D16" t="s">
-        <v>797</v>
-      </c>
-      <c r="E16" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>759</v>
-      </c>
-      <c r="B17" t="s">
-        <v>760</v>
-      </c>
-      <c r="C17" t="s">
-        <v>761</v>
-      </c>
-      <c r="D17" t="s">
-        <v>762</v>
-      </c>
-      <c r="E17" t="s">
-        <v>763</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE91C49D-AC90-484D-977A-FE1BA9A7FAF7}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="35.77734375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>816</v>
-      </c>
-      <c r="B1" t="s">
-        <v>879</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>817</v>
-      </c>
-      <c r="D1" t="s">
-        <v>818</v>
-      </c>
-      <c r="E1" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>820</v>
-      </c>
-      <c r="B2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D2" t="s">
-        <v>823</v>
-      </c>
-      <c r="E2" t="s">
-        <v>824</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>825</v>
-      </c>
-      <c r="B3" t="s">
-        <v>819</v>
-      </c>
-      <c r="C3" t="s">
-        <v>818</v>
-      </c>
-      <c r="D3" t="s">
-        <v>879</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>827</v>
-      </c>
-      <c r="B4" t="s">
-        <v>880</v>
-      </c>
-      <c r="C4" t="s">
-        <v>881</v>
-      </c>
-      <c r="D4" t="s">
-        <v>882</v>
-      </c>
-      <c r="E4" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>886</v>
-      </c>
-      <c r="B5" t="s">
-        <v>881</v>
-      </c>
-      <c r="C5" t="s">
-        <v>880</v>
-      </c>
-      <c r="D5" t="s">
-        <v>882</v>
-      </c>
-      <c r="E5" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>826</v>
-      </c>
-      <c r="B6" t="s">
-        <v>884</v>
-      </c>
-      <c r="C6" t="s">
-        <v>828</v>
-      </c>
-      <c r="D6" t="s">
-        <v>885</v>
-      </c>
-      <c r="E6" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>829</v>
-      </c>
-      <c r="B7" t="s">
-        <v>830</v>
-      </c>
-      <c r="C7" t="s">
-        <v>817</v>
-      </c>
-      <c r="D7" t="s">
-        <v>776</v>
-      </c>
-      <c r="E7" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>832</v>
-      </c>
-      <c r="B8" t="s">
-        <v>817</v>
-      </c>
-      <c r="C8" t="s">
-        <v>830</v>
-      </c>
-      <c r="D8" t="s">
-        <v>776</v>
-      </c>
-      <c r="E8" t="s">
-        <v>831</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C1" r:id="rId1" display="\\frac'\\Delta s}{\\Delta m}" xr:uid="{9EBE9598-93DE-44B1-9E12-35D0695E2A1D}"/>
-    <hyperlink ref="E3" r:id="rId2" display="\\frac'\\Delta s}{\\Delta m}" xr:uid="{603A108F-9A9B-4540-BB60-AF31490918AF}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5E6206-03F2-4F89-8196-C8D209084E58}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6304,7 +8770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E5C0D07-AEB7-49FA-8F13-9A57FFFF9D49}">
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6645,7 +9111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E926785D-7CB9-4E04-886B-7496664031F1}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -6950,7 +9416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BDA72-B842-492B-A703-AFCE8612FDB2}">
   <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7762,7 +10228,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46F09D7F-6627-424B-99D1-DA5E4F05551C}">
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8213,7 +10679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89BD9279-0741-45B2-95DF-8087870757BD}">
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8596,7 +11062,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{661E2F8C-8310-4E98-B7DA-C401EB6B1BC7}">
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9045,258 +11511,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B40EA02D-DC56-4A89-98F7-42A234EB60C7}">
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="25.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>536</v>
-      </c>
-      <c r="B1" t="s">
-        <v>489</v>
-      </c>
-      <c r="C1" t="s">
-        <v>490</v>
-      </c>
-      <c r="D1" t="s">
-        <v>491</v>
-      </c>
-      <c r="E1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B2" t="s">
-        <v>494</v>
-      </c>
-      <c r="C2" t="s">
-        <v>495</v>
-      </c>
-      <c r="D2" t="s">
-        <v>496</v>
-      </c>
-      <c r="E2" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B3" t="s">
-        <v>508</v>
-      </c>
-      <c r="C3" t="s">
-        <v>502</v>
-      </c>
-      <c r="D3" t="s">
-        <v>499</v>
-      </c>
-      <c r="E3" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>501</v>
-      </c>
-      <c r="B4" t="s">
-        <v>502</v>
-      </c>
-      <c r="C4" t="s">
-        <v>508</v>
-      </c>
-      <c r="D4" t="s">
-        <v>503</v>
-      </c>
-      <c r="E4" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>505</v>
-      </c>
-      <c r="B5" t="s">
-        <v>506</v>
-      </c>
-      <c r="C5" t="s">
-        <v>507</v>
-      </c>
-      <c r="D5" t="s">
-        <v>508</v>
-      </c>
-      <c r="E5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="B6" t="s">
-        <v>511</v>
-      </c>
-      <c r="C6" t="s">
-        <v>512</v>
-      </c>
-      <c r="D6" t="s">
-        <v>513</v>
-      </c>
-      <c r="E6" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>865</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="C7" t="s">
-        <v>516</v>
-      </c>
-      <c r="D7" t="s">
-        <v>517</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>524</v>
-      </c>
-      <c r="B8" t="s">
-        <v>519</v>
-      </c>
-      <c r="C8" t="s">
-        <v>520</v>
-      </c>
-      <c r="D8" t="s">
-        <v>521</v>
-      </c>
-      <c r="E8" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>523</v>
-      </c>
-      <c r="B9" t="s">
-        <v>521</v>
-      </c>
-      <c r="C9" t="s">
-        <v>520</v>
-      </c>
-      <c r="D9" t="s">
-        <v>519</v>
-      </c>
-      <c r="E9" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>525</v>
-      </c>
-      <c r="B10" t="s">
-        <v>522</v>
-      </c>
-      <c r="C10" t="s">
-        <v>521</v>
-      </c>
-      <c r="D10" t="s">
-        <v>519</v>
-      </c>
-      <c r="E10" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>526</v>
-      </c>
-      <c r="B11" t="s">
-        <v>527</v>
-      </c>
-      <c r="C11" t="s">
-        <v>531</v>
-      </c>
-      <c r="D11" t="s">
-        <v>528</v>
-      </c>
-      <c r="E11" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>530</v>
-      </c>
-      <c r="B12" t="s">
-        <v>531</v>
-      </c>
-      <c r="C12" t="s">
-        <v>515</v>
-      </c>
-      <c r="D12" t="s">
-        <v>532</v>
-      </c>
-      <c r="E12" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>533</v>
-      </c>
-      <c r="B13" t="s">
-        <v>534</v>
-      </c>
-      <c r="C13" t="s">
-        <v>535</v>
-      </c>
-      <c r="D13" t="s">
-        <v>531</v>
-      </c>
-      <c r="E13" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>585</v>
-      </c>
-      <c r="B14" t="s">
-        <v>586</v>
-      </c>
-      <c r="C14" t="s">
-        <v>587</v>
-      </c>
-      <c r="D14" t="s">
-        <v>588</v>
-      </c>
-      <c r="E14" t="s">
-        <v>589</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A6" r:id="rId1" xr:uid="{FEC73E89-5B41-4E91-B6E2-A2658C373BCC}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>